--- a/AAII_Financials/Yearly/BHR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BHR_YR_FIN.xlsx
@@ -1008,13 +1008,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-24000</v>
+        <v>-22200</v>
       </c>
       <c r="E14" s="3">
-        <v>-88100</v>
+        <v>-82000</v>
       </c>
       <c r="F14" s="3">
-        <v>-2300</v>
+        <v>1200</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
